--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486535_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486535_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4534</v>
+        <v>6.323</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5432</v>
+        <v>4.3025</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9103</v>
+        <v>2.0205</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1949</v>
+        <v>5.9155</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0833</v>
+        <v>-0.347</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1116</v>
+        <v>6.2625</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4031</v>
+        <v>6.4552</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4851</v>
+        <v>0.2372</v>
       </c>
       <c r="L2" t="n">
-        <v>0.918</v>
+        <v>6.2179</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2082</v>
+        <v>-0.5397</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4018</v>
+        <v>-0.5843</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1936</v>
+        <v>0.0446</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.5225</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>5.0405</v>
+        <v>0.712</v>
       </c>
       <c r="T2" t="n">
-        <v>4.1194</v>
+        <v>0.1094</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9211</v>
+        <v>0.6026</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.3045</v>
+        <v>-0.7395</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0207</v>
+        <v>-0.7395</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.479</v>
+        <v>5.6009</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5202</v>
+        <v>5.153</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9589</v>
+        <v>0.4479</v>
       </c>
       <c r="G3" t="n">
-        <v>5.9155</v>
+        <v>3.1949</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.347</v>
+        <v>2.0833</v>
       </c>
       <c r="I3" t="n">
-        <v>6.2625</v>
+        <v>1.1116</v>
       </c>
       <c r="J3" t="n">
-        <v>6.4552</v>
+        <v>3.4031</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2372</v>
+        <v>2.4851</v>
       </c>
       <c r="L3" t="n">
-        <v>6.2179</v>
+        <v>0.918</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5397</v>
+        <v>-0.2082</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5843</v>
+        <v>-0.4018</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0446</v>
+        <v>0.1936</v>
       </c>
       <c r="P3" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.132</v>
+        <v>2.188</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6729000000000001</v>
+        <v>1.7293</v>
       </c>
       <c r="U3" t="n">
-        <v>0.541</v>
+        <v>0.4587</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7395</v>
+        <v>-1.3045</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.7395</v>
+        <v>0.0207</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9771</v>
+        <v>2.8981</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3832</v>
+        <v>2.4892</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5939</v>
+        <v>0.4089</v>
       </c>
       <c r="G4" t="n">
         <v>0.2918</v>
@@ -766,13 +766,13 @@
         <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9028</v>
+        <v>0.8238</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4456</v>
+        <v>0.5516</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4571</v>
+        <v>0.2722</v>
       </c>
       <c r="V4" t="n">
         <v>1.13</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3511</v>
+        <v>2.7105</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4179</v>
+        <v>0.8799</v>
       </c>
       <c r="F5" t="n">
-        <v>1.769</v>
+        <v>1.8306</v>
       </c>
       <c r="G5" t="n">
         <v>1.0278</v>
@@ -844,13 +844,13 @@
         <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7845</v>
+        <v>0.575</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2209</v>
+        <v>0.0769</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4364</v>
+        <v>0.4981</v>
       </c>
       <c r="V5" t="n">
         <v>1.3252</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7978</v>
+        <v>1.1138</v>
       </c>
       <c r="E6" t="n">
-        <v>0.288</v>
+        <v>0.5115</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5098</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0.8852</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5224</v>
+        <v>-0.2064</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.399</v>
+        <v>-0.1754</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1234</v>
+        <v>-0.031</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3676</v>
+        <v>0.3652</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4703</v>
+        <v>1.3084</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8379</v>
+        <v>-0.9433</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1686</v>
+        <v>0.0735</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7939000000000001</v>
+        <v>-0.8668</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3747</v>
+        <v>0.9403</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3577</v>
+        <v>1.0068</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5607</v>
+        <v>0.2801</v>
       </c>
       <c r="L7" t="n">
-        <v>2.797</v>
+        <v>0.7267</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1891</v>
+        <v>-0.9333</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7668</v>
+        <v>-1.1468</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4224</v>
+        <v>0.2136</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.4801</v>
+        <v>1.0875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.7852</v>
+        <v>-0.2175</v>
       </c>
       <c r="R7" t="n">
         <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2691</v>
+        <v>0.3341</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.5191</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3714</v>
+        <v>-0.1851</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.397</v>
+        <v>-0.0448</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7929</v>
+        <v>0.7623</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1899</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0735</v>
+        <v>3.1686</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8668</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9403</v>
+        <v>2.3747</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0068</v>
+        <v>4.3577</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2801</v>
+        <v>1.5607</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7267</v>
+        <v>2.797</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9333</v>
+        <v>-1.1891</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1468</v>
+        <v>-0.7668</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2136</v>
+        <v>-0.4224</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0875</v>
+        <v>-3.4801</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2175</v>
+        <v>-4.7852</v>
       </c>
       <c r="R8" t="n">
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.428</v>
+        <v>1.5919</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0036</v>
+        <v>1.1897</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4317</v>
+        <v>0.4023</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7763</v>
+        <v>-0.2368</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.225</v>
+        <v>0.222</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5513</v>
+        <v>-0.4588</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2539</v>
@@ -1156,13 +1156,13 @@
         <v>0.2175</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5224</v>
+        <v>0.0171</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.137</v>
+        <v>0.31</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3854</v>
+        <v>-0.2929</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6468</v>
+        <v>-1.2884</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2131</v>
+        <v>0.3249</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8599</v>
+        <v>-1.6133</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3387</v>
@@ -1234,13 +1234,13 @@
         <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3956</v>
+        <v>-0.0373</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.113</v>
+        <v>-0.0012</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2826</v>
+        <v>-0.0361</v>
       </c>
       <c r="V10" t="n">
         <v>-1.13</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3003</v>
+        <v>-2.5285</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9186</v>
+        <v>-3.9618</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6183</v>
+        <v>1.4333</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3826</v>
@@ -1312,13 +1312,13 @@
         <v>1.9576</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5603</v>
+        <v>1.3321</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2077</v>
+        <v>1.1645</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3526</v>
+        <v>0.1676</v>
       </c>
       <c r="V11" t="n">
         <v>0.1745</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.5704</v>
+        <v>14.913</v>
       </c>
       <c r="E12" t="n">
-        <v>11.6494</v>
+        <v>11.9919</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9212</v>
+        <v>2.9211</v>
       </c>
       <c r="G12" t="n">
         <v>10.5821</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0753000000000002</v>
+        <v>0.07530000000000009</v>
       </c>
       <c r="I12" t="n">
         <v>10.5066</v>
@@ -1372,13 +1372,13 @@
         <v>10.3832</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.6198</v>
+        <v>-7.619800000000001</v>
       </c>
       <c r="N12" t="n">
         <v>-7.743300000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1235000000000002</v>
+        <v>0.1235</v>
       </c>
       <c r="P12" t="n">
         <v>-0.0001000000000001</v>
@@ -1390,13 +1390,13 @@
         <v>13.0503</v>
       </c>
       <c r="S12" t="n">
-        <v>6.9878</v>
+        <v>7.330299999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>5.1312</v>
+        <v>5.4739</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8565</v>
+        <v>1.8564</v>
       </c>
       <c r="V12" t="n">
         <v>-2.9995</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.348</v>
+        <v>1.9966</v>
       </c>
       <c r="E13" t="n">
-        <v>0.743</v>
+        <v>0.6312</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6051</v>
+        <v>1.3654</v>
       </c>
       <c r="G13" t="n">
         <v>2.4393</v>
@@ -1468,13 +1468,13 @@
         <v>1.5225</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1783</v>
+        <v>-0.5296</v>
       </c>
       <c r="T13" t="n">
-        <v>0.08409999999999999</v>
+        <v>-0.0276</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2624</v>
+        <v>-0.502</v>
       </c>
       <c r="V13" t="n">
         <v>0.7395</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4448</v>
+        <v>0.3367</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6361</v>
+        <v>0.0717</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1913</v>
+        <v>0.2649</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6615</v>
+        <v>-0.4517</v>
       </c>
       <c r="H14" t="n">
-        <v>1.098</v>
+        <v>0.1579</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.7595</v>
+        <v>-0.6096</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8465</v>
+        <v>1.6219</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3787</v>
+        <v>0.4927</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5323</v>
+        <v>1.1292</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.508</v>
+        <v>-2.0736</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2808</v>
+        <v>-0.3348</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2272</v>
+        <v>-1.7388</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3717</v>
+        <v>-0.9082</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4867</v>
+        <v>-0.4626</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8584000000000001</v>
+        <v>-0.4455</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3904</v>
+        <v>1.479</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.479</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1168</v>
+        <v>-0.1692</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2636</v>
+        <v>0.9656</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1468</v>
+        <v>-1.1348</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4517</v>
+        <v>-0.6615</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1579</v>
+        <v>1.098</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6096</v>
+        <v>-1.7595</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6219</v>
+        <v>1.8465</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4927</v>
+        <v>2.3787</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1292</v>
+        <v>-0.5323</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0736</v>
+        <v>-2.508</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3348</v>
+        <v>-1.2808</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.7388</v>
+        <v>-1.2272</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>1.305</v>
+        <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3616</v>
+        <v>-0.9857</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.1838</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5637</v>
+        <v>-0.8018</v>
       </c>
       <c r="V15" t="n">
-        <v>1.479</v>
+        <v>0.3904</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X15" t="n">
-        <v>1.479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>H. ATENCIA SUAREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2844</v>
+        <v>-1.8689</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8156</v>
+        <v>-0.8847</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4688</v>
+        <v>-0.9842</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3475</v>
+        <v>-4.3656</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7451</v>
+        <v>-1.9917</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0925</v>
+        <v>-2.3738</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5596</v>
+        <v>-2.7565</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4449</v>
+        <v>-1.4409</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1147</v>
+        <v>-1.3156</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9071</v>
+        <v>-1.6091</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6998</v>
+        <v>-0.5508</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2073</v>
+        <v>-1.0583</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.7401</v>
+        <v>1.7401</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6079</v>
+        <v>-1.5033</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6922</v>
+        <v>-0.3881</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0843</v>
+        <v>-1.1152</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1952</v>
+        <v>2.2599</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1952</v>
+        <v>2.2599</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. FELIU ESPEJO</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.137</v>
+        <v>-2.0158</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9436</v>
+        <v>-1.3447</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1934</v>
+        <v>-0.6712</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4689</v>
+        <v>0.1353</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2618</v>
+        <v>1.18</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7307</v>
+        <v>-1.0447</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0294</v>
+        <v>1.7021</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9767</v>
+        <v>2.4089</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0527</v>
+        <v>-0.7068</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4983</v>
+        <v>-1.5668</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7149</v>
+        <v>-1.2289</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7834</v>
+        <v>-0.3379</v>
       </c>
       <c r="P17" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-2.1751</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-3.2626</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>0.507</v>
+        <v>-0.3464</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2896</v>
+        <v>-0.1322</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2174</v>
+        <v>-0.2142</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.9347</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ROBERTS</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1539</v>
+        <v>-2.0332</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7168</v>
+        <v>-1.3744</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.437</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.9827</v>
+        <v>-0.3475</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1898</v>
+        <v>0.7451</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7929</v>
+        <v>-1.0925</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2494</v>
+        <v>1.5596</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3259</v>
+        <v>1.4449</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0765</v>
+        <v>0.1147</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7333</v>
+        <v>-1.9071</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8639</v>
+        <v>-0.6998</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8694</v>
+        <v>-1.2073</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0875</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2587</v>
+        <v>-0.1409</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4675</v>
+        <v>0.1334</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2087</v>
+        <v>-0.2743</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>J. ROBERTS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4076</v>
+        <v>-2.2938</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6799</v>
+        <v>-1.6051</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7277</v>
+        <v>-0.6887</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1353</v>
+        <v>-2.9827</v>
       </c>
       <c r="H19" t="n">
-        <v>1.18</v>
+        <v>-2.1898</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0447</v>
+        <v>-0.7929</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7021</v>
+        <v>-1.2494</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4089</v>
+        <v>-1.3259</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7068</v>
+        <v>0.0765</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5668</v>
+        <v>-1.7333</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2289</v>
+        <v>-0.8639</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3379</v>
+        <v>-0.8694</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7382</v>
+        <v>-0.3987</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4675</v>
+        <v>-0.3557</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2708</v>
+        <v>-0.043</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9347</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. ATENCIA SUAREZ</t>
+          <t>J. FELIU ESPEJO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9723</v>
+        <v>-2.3541</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4435</v>
+        <v>-1.2789</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5288</v>
+        <v>-1.0752</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.3656</v>
+        <v>-0.4689</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9917</v>
+        <v>0.2618</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.3738</v>
+        <v>-0.7307</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.7565</v>
+        <v>2.0294</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4409</v>
+        <v>0.9767</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3156</v>
+        <v>1.0527</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6091</v>
+        <v>-2.4983</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5508</v>
+        <v>-0.7149</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0583</v>
+        <v>-1.7834</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7401</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.6067</v>
+        <v>0.2899</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9469</v>
+        <v>-0.0457</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.6598</v>
+        <v>0.3356</v>
       </c>
       <c r="V20" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.2914</v>
+        <v>-4.6787</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5628</v>
+        <v>1.8981</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.8542</v>
+        <v>-6.5768</v>
       </c>
       <c r="G21" t="n">
         <v>-3.8789</v>
@@ -2092,13 +2092,13 @@
         <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5876</v>
+        <v>-0.9749</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7294</v>
+        <v>-0.3941</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8581</v>
+        <v>-0.5807</v>
       </c>
       <c r="V21" t="n">
         <v>-1.13</v>
@@ -2125,31 +2125,31 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-14.5706</v>
+        <v>-13.0804</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9211</v>
+        <v>-2.921199999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.6493</v>
+        <v>-10.1594</v>
       </c>
       <c r="G22" t="n">
         <v>-10.5822</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.07539999999999925</v>
+        <v>-0.07539999999999969</v>
       </c>
       <c r="I22" t="n">
         <v>-10.5066</v>
       </c>
       <c r="J22" t="n">
-        <v>7.6198</v>
+        <v>7.619800000000001</v>
       </c>
       <c r="K22" t="n">
         <v>7.742999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1235000000000002</v>
+        <v>-0.1235000000000001</v>
       </c>
       <c r="M22" t="n">
         <v>-18.202</v>
@@ -2170,13 +2170,13 @@
         <v>13.0502</v>
       </c>
       <c r="S22" t="n">
-        <v>-6.9879</v>
+        <v>-5.4978</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.8566</v>
+        <v>-1.8564</v>
       </c>
       <c r="U22" t="n">
-        <v>-5.1314</v>
+        <v>-3.6411</v>
       </c>
       <c r="V22" t="n">
         <v>2.999300000000001</v>
